--- a/handouts/poll-bank.xlsx
+++ b/handouts/poll-bank.xlsx
@@ -445,12 +445,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Session time</t>
+          <t>Session</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Baseline only. Re-ask at 16:20 in a different form (the confidence question).</t>
+          <t>Baseline only. Re-ask at the close in a different form (the confidence question).</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>Session 3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>Session 3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Chugh et al. 2026. ₹54,881 is the ICER for VIA screening from Block 1, a distractor on purpose.</t>
+          <t>Chugh et al. 2026. ₹54,881 is the ICER for VIA screening from Session 2, a distractor on purpose.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>Session 3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>Session 4</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>Session 4</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>Session 4</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>Session 5</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>Session 5</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>Session 5</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>Session 6</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>Session 6</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,400 ÷ 0.13. ₹204 is the average ratio from Block 3B: total cost over total QALYs, meaningless for a decision.</t>
+          <t>3,400 ÷ 0.13. ₹204 is the average ratio from Session 6: total cost over total QALYs, meaningless for a decision.</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>Session 6</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>Session 7</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>Session 7</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>Session 8</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>Session 8</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>Session 8</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Compare with the 09:40 baseline. Opinion; no right answer.</t>
+          <t>Compare with the Session 1 baseline. Opinion; no right answer.</t>
         </is>
       </c>
     </row>

--- a/handouts/poll-bank.xlsx
+++ b/handouts/poll-bank.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Thresholds, opportunity cost and budget impact</t>
+          <t>Framing the question</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -786,27 +786,27 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The rule that cost per DALY below one to three times GDP per capita is cost-effective is:</t>
+          <t>The Indian Reference Case asks for which base-case perspective?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>India's official threshold</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>WHO's current recommendation</t>
+          <t>Payer only</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>a heuristic that its own authors have argued should be retired</t>
+          <t>Abridged societal</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>derived from India's health budget</t>
+          <t>Full societal, including productivity</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Demand-side, not linked to any budget. Two papers in the pack still use it; ask whether it changes their verdict.</t>
+          <t>Payer and patient direct costs, including out-of-pocket. Payer perspective reported separately.</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Thresholds, opportunity cost and budget impact</t>
+          <t>Framing the question</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -841,27 +841,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>India's recent estimate of willingness to pay per QALY is closest to:</t>
+          <t>The comparator in an Indian evaluation should normally be:</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>₹54,881</t>
+          <t>doing nothing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>₹2,12,307</t>
+          <t>current practice</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>₹20,000</t>
+          <t>the best practice anywhere in the world</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>₹10,00,000</t>
+          <t>the cheapest option available</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Chugh et al. 2026. ₹54,881 is the ICER for VIA screening from Session 2, a distractor on purpose.</t>
+          <t>Do-nothing is right only when it is genuinely what happens now. A weak comparator flatters every result downstream.</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Thresholds, opportunity cost and budget impact</t>
+          <t>Framing the question</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -896,27 +896,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>An intervention is cost-effective. Which question does that leave unanswered?</t>
+          <t>HPV vaccination of 14-year-olds evaluated over a one-year horizon would look:</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Is it good value per QALY?</t>
+          <t>cost-effective</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Can we afford it for everyone this year?</t>
+          <t>like a waste of money</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Is its ICER below the threshold?</t>
+          <t>unaffected by the horizon</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Does it produce health?</t>
+          <t>cost-saving</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Budget impact is a separate test. Cost-effective is not the same as funded.</t>
+          <t>All the cost falls in year one; the cancers prevented come decades later. The horizon decides the answer.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Framing the question</t>
+          <t>Outcomes, discounting and the ICER</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1116,37 +1116,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>The Indian Reference Case asks for which base-case perspective?</t>
+          <t>Two years lived at a utility of 0.5 are worth how many QALYs?</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Payer only</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Abridged societal</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Full societal, including productivity</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Payer and patient direct costs, including out-of-pocket. Payer perspective reported separately.</t>
+          <t>0.5 × 2. The QALY's power and its controversy in one line.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Framing the question</t>
+          <t>Outcomes, discounting and the ICER</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>The comparator in an Indian evaluation should normally be:</t>
+          <t>A programme costs ₹3,400 more than the comparator and gains 0.13 QALYs. What is the ICER?</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>doing nothing</t>
+          <t>₹204 per QALY</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>current practice</t>
+          <t>₹26,154 per QALY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>the best practice anywhere in the world</t>
+          <t>₹4,420 per QALY</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>the cheapest option available</t>
+          <t>₹442 per QALY</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Do-nothing is right only when it is genuinely what happens now. A weak comparator flatters every result downstream.</t>
+          <t>3,400 ÷ 0.13. ₹204 is the average ratio, total cost over total QALYs, meaningless for a decision.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Framing the question</t>
+          <t>Outcomes, discounting and the ICER</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1226,27 +1226,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>HPV vaccination of 14-year-olds evaluated over a one-year horizon would look:</t>
+          <t>India's discount rate for costs and outcomes is:</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>cost-effective</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>like a waste of money</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unaffected by the horizon</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>cost-saving</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>All the cost falls in year one; the cancers prevented come decades later. The horizon decides the answer.</t>
+          <t>3%, varied from 0 to 5% in sensitivity analysis, with undiscounted results also reported.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Outcomes, discounting and the ICER</t>
+          <t>Thresholds, opportunity cost and budget impact</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Two years lived at a utility of 0.5 are worth how many QALYs?</t>
+          <t>The rule that cost per DALY below one to three times GDP per capita is cost-effective is:</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>India's official threshold</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>WHO's current recommendation</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>a heuristic that its own authors have argued should be retired</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>derived from India's health budget</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0.5 × 2. The QALY's power and its controversy in one line.</t>
+          <t>Demand-side, not linked to any budget. Two papers in the pack still use it; ask whether it changes their verdict.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Outcomes, discounting and the ICER</t>
+          <t>Thresholds, opportunity cost and budget impact</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1336,27 +1336,27 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>A programme costs ₹3,400 more than the comparator and gains 0.13 QALYs. What is the ICER?</t>
+          <t>India's recent estimate of willingness to pay per QALY is closest to:</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>₹204 per QALY</t>
+          <t>₹54,881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>₹26,154 per QALY</t>
+          <t>₹2,12,307</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>₹4,420 per QALY</t>
+          <t>₹20,000</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>₹442 per QALY</t>
+          <t>₹10,00,000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,400 ÷ 0.13. ₹204 is the average ratio from Session 6: total cost over total QALYs, meaningless for a decision.</t>
+          <t>Chugh et al. 2026. ₹54,881 is the ICER for VIA screening from Session 2, a distractor on purpose.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Outcomes, discounting and the ICER</t>
+          <t>Thresholds, opportunity cost and budget impact</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>India's discount rate for costs and outcomes is:</t>
+          <t>An intervention is cost-effective. Which question does that leave unanswered?</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Is it good value per QALY?</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>Can we afford it for everyone this year?</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>Is its ICER below the threshold?</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>Does it produce health?</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3%, varied from 0 to 5% in sensitivity analysis, with undiscounted results also reported.</t>
+          <t>Budget impact is a separate test. Cost-effective is not the same as funded.</t>
         </is>
       </c>
     </row>
